--- a/data/trans_orig/P79A3_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P79A3_2023-Habitat-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>803</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>803</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,27 +1103,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1538</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>8606</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -1181,27 +1181,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>5915</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>704</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1226,12 +1226,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>6619</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>941</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1657</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>74,86%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2797</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>477</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14497</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>880</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1346</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,52%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6079</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11812</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13255</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10586</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9639</t>
+          <t>10419</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6926</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14207</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>21469</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>19702</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>22950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7315</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>41,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>24634</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>78,9%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>24371</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>42105</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
